--- a/data/describe/few_shot/final_summary/messages_dog.xlsx
+++ b/data/describe/few_shot/final_summary/messages_dog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\input_final_summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9084F9-0E32-4F34-AE25-22BF48B8E29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAF619B-DBA7-41D8-9E08-977C794C25D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40635" yWindow="2520" windowWidth="33900" windowHeight="17430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30570" yWindow="1755" windowWidth="22980" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>User</t>
   </si>
@@ -34,18 +34,6 @@
   </si>
   <si>
     <t>What does it mean when a dog is described as social and adaptable?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Now your task is to provide a description of a cluster.
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. </t>
-  </si>
-  <si>
-    <t>Understood. Please provide the cluster descriptions.</t>
   </si>
   <si>
     <t>What does it mean when a dog is described as active and engaged?</t>
@@ -116,6 +104,31 @@
 Now do the same thing with the following: ```Members of this cluster can be described as:  normal on active and engaged,  slightly high on sociable and adaptable,  normal on stalwart and vigilant,  quite high on keen guardian´´´</t>
   </si>
   <si>
+    <t>This cluster describes dogs that are highly protective and good with people, but tend to have a lower energy level and may struggle with other canine companions.
+Their strengths lie in their stalwart and vigilant nature, making them natural protectors of their domain, and their sociable and adaptable disposition, allowing them to be affectionate with families and charming with young children.
+However, a notable weakness is their calm and relaxed demeanor, which suggests less adaptability and trainability, coupled with a relatively low congeniality that means they might not get along well with other canine companions.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are predominantly calm and relaxed, favoring a quiet life with low energy, and while not highly independent, they also aren't strongly characterized by a moderate, serene demeanor. Their main strengths include their preference for a quiet, low-energy life, making them suitable companions for those seeking a less demanding pet, and they generally exhibit average sociability with other dogs. However, their high calm and relaxed nature means they may be less adaptable to new situations and challenging to train, and they are less likely to display a moderate, balanced energy level, potentially leaning towards a more sluggish disposition.</t>
+  </si>
+  <si>
+    <t>Now, your next task is to describe a specific dog based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the dog. The first sentence should use varied language to give an overview of the dog. The second sentence should describe the dog's specific strengths based on the metrics. The third sentence should describe aspects in which the dog is average and/or weak based on the statistics. Finally, summarize the dog with a single concluding statement. Here is the statistical description of the dog: ```Retrievers (Labrador) is extremely low on active and engaged. In particular, Retrievers (Labrador) indicates that Mental stimulation needs (on a scale of '1' to '5'). Retrievers (Labrador) is quite high on sociable and adaptable. Retrievers (Labrador) is quite low on solitary and independent. Retrievers (Labrador) is very low on congenial and abundant. In particular, Retrievers (Labrador) indicates that Drooling level (on a scale of '1' to '5'). ´´´ Here is the informative description of a dog belongs to: ```Retrievers (Labrador) is steadfast guard with the following characteristics: This cluster describes dogs that are generally low in energy and engagement, not particularly mellow, and are not very social with other dogs, but they do possess a degree of protective instinct. Their primary strength lies in their slightly elevated stalwart and vigilant trait, indicating a capacity for watchful and protective behavior that can be an asset for their home. However, they exhibit significant weaknesses in being quite low on active and engaged, meaning they are neither playful, bursting with energy, eager for mental stimulation, adaptable, nor easily trainable, and they tend to be less congenial with other canines.´´´</t>
+  </si>
+  <si>
+    <t>Labrador Retrievers are renowned for their affectionate nature towards people, yet they are dogs with remarkably low energy demands and limited interest in intense mental stimulation or extensive canine socializing. Their primary strength lies in their high sociability and adaptability with human families, making them charming and adjustable companions, coupled with a subtle underlying protective instinct. However, they are extremely low in active engagement and mental stimulation needs, tend to be less congenial with other dogs, and also exhibit a very low drooling level. Consequently, the Labrador Retriever is a loyal, human-centric dog that thrives in a calm environment rather than one requiring high energy, constant activity, or broad canine social interaction.</t>
+  </si>
+  <si>
+    <t>Thats really good. You truly understand the factors and names. 
+Now your task is to provide a description of a cluster.
+Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
+For each cluster, write a concise summary based on the available information.
+The first sentence should give an overview of the cluster. 
+The second sentence should describe the cluster’s specific strengths based on the available information.
+The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
+I will provided you with the cluster description and you will return the summary. 
+Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  normal on active and engaged,  relatively high on sociable and adaptable,  quite low on solitary and independent,  slightly low on congenial and abundant´´´</t>
+  </si>
+  <si>
     <t>This cluster describes dogs that are highly sociable and adaptable with humans, displaying average energy levels, and are generally easy to maintain.
 Their strengths include significant affection for their human families, charm with young children, and remarkable ease in adapting to new situations, alongside being less prone to shedding and drooling.
 However, they might exhibit a nuanced social dynamic with other dogs, as they are not solitary but are also slightly less congenial in canine companionship.</t>
@@ -126,23 +139,9 @@
 However, they exhibit significant weaknesses in being quite low on active and engaged, meaning they are neither playful, bursting with energy, eager for mental stimulation, adaptable, nor easily trainable, and they tend to be less congenial with other canines.</t>
   </si>
   <si>
-    <t>This cluster describes dogs that are highly protective and good with people, but tend to have a lower energy level and may struggle with other canine companions.
-Their strengths lie in their stalwart and vigilant nature, making them natural protectors of their domain, and their sociable and adaptable disposition, allowing them to be affectionate with families and charming with young children.
-However, a notable weakness is their calm and relaxed demeanor, which suggests less adaptability and trainability, coupled with a relatively low congeniality that means they might not get along well with other canine companions.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are predominantly calm and relaxed, favoring a quiet life with low energy, and while not highly independent, they also aren't strongly characterized by a moderate, serene demeanor. Their main strengths include their preference for a quiet, low-energy life, making them suitable companions for those seeking a less demanding pet, and they generally exhibit average sociability with other dogs. However, their high calm and relaxed nature means they may be less adaptable to new situations and challenging to train, and they are less likely to display a moderate, balanced energy level, potentially leaning towards a more sluggish disposition.</t>
-  </si>
-  <si>
     <t>This cluster describes dogs that are exceptionally protective and watchful, paired with a sociable and adaptable nature, while maintaining an average level of general activity.
 Their primary strengths lie in their quite high keen guardian instinct, making them highly vigilant protectors of their loved ones and territory, complemented by their slightly high sociability and adaptability, which allows them to be affectionate with families and adjust well to new surroundings.
 However, their 'normal' levels of active and engaged behavior and stalwart and vigilant traits suggest they may not always be bursting with energy or constantly demanding mental stimulation, and their protective nature, while strong, isn't necessarily paired with the most extreme, unwavering guarding beyond their inherent watchfulness.</t>
-  </si>
-  <si>
-    <t>Now, your next task is to describe a specific dog based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the dog. The first sentence should use varied language to give an overview of the dog. The second sentence should describe the dog's specific strengths based on the metrics. The third sentence should describe aspects in which the dog is average and/or weak based on the statistics. Finally, summarize the dog with a single concluding statement. Here is the statistical description of the dog: ```Retrievers (Labrador) is extremely low on active and engaged. In particular, Retrievers (Labrador) indicates that Mental stimulation needs (on a scale of '1' to '5'). Retrievers (Labrador) is quite high on sociable and adaptable. Retrievers (Labrador) is quite low on solitary and independent. Retrievers (Labrador) is very low on congenial and abundant. In particular, Retrievers (Labrador) indicates that Drooling level (on a scale of '1' to '5'). ´´´ Here is the informative description of a dog belongs to: ```Retrievers (Labrador) is steadfast guard with the following characteristics: This cluster describes dogs that are generally low in energy and engagement, not particularly mellow, and are not very social with other dogs, but they do possess a degree of protective instinct. Their primary strength lies in their slightly elevated stalwart and vigilant trait, indicating a capacity for watchful and protective behavior that can be an asset for their home. However, they exhibit significant weaknesses in being quite low on active and engaged, meaning they are neither playful, bursting with energy, eager for mental stimulation, adaptable, nor easily trainable, and they tend to be less congenial with other canines.´´´</t>
-  </si>
-  <si>
-    <t>Labrador Retrievers are renowned for their affectionate nature towards people, yet they are dogs with remarkably low energy demands and limited interest in intense mental stimulation or extensive canine socializing. Their primary strength lies in their high sociability and adaptability with human families, making them charming and adjustable companions, coupled with a subtle underlying protective instinct. However, they are extremely low in active engagement and mental stimulation needs, tend to be less congenial with other dogs, and also exhibit a very low drooling level. Consequently, the Labrador Retriever is a loyal, human-centric dog that thrives in a calm environment rather than one requiring high energy, constant activity, or broad canine social interaction.</t>
   </si>
 </sst>
 </file>
@@ -525,26 +524,26 @@
     </row>
     <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
@@ -552,95 +551,95 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/final_summary/messages_dog.xlsx
+++ b/data/describe/few_shot/final_summary/messages_dog.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAF619B-DBA7-41D8-9E08-977C794C25D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9854ACEF-BCF9-416C-BA38-0A5F4C8F9589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30570" yWindow="1755" windowWidth="22980" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="53295" yWindow="2640" windowWidth="23370" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>User</t>
   </si>
@@ -33,122 +33,114 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a dog is described as social and adaptable?</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as active and engaged?</t>
-  </si>
-  <si>
-    <t>An active and engaged dog is incredibly playful, bursting with energy, and always eager for mental stimulation. They are also highly adaptable to new situations and quite trainable, ready to learn and respond.</t>
+    <t>What does it mean when a dog is described as playful and energetic?</t>
+  </si>
+  <si>
+    <t>When a dog is described as playful and energetic, it means they are truly a bundle of joy, bursting with playfulness and high energy, always eager for fun and in need of exciting mental challenges to keep their clever mind engaged. These lively pups are also incredibly adaptable, ready to embrace new experiences, and respond well to training.</t>
   </si>
   <si>
     <t>What does it mean when a dog is described as calm and relaxed?</t>
   </si>
   <si>
-    <t>A dog described as calm and relaxed isn't one for endless games or constant mental puzzles; they tend to have a lower energy level and prefer a quiet life. You might also find them to be less adaptable to new situations and not the easiest to train.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as mellow and serene?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> When a dog is described as mellow and serene, it means they have a comfortable, moderate energy level – not overly excitable, but not sluggish either.</t>
-  </si>
-  <si>
-    <t>Sociable and adaptable dogs are truly people-pleasers, showing plenty of affection for their human families and charming young children with their gentle nature. They also adjust to new surroundings and experiences with remarkable ease, and you might notice their drooling level as a minor characteristic.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as solitary and independent?</t>
-  </si>
-  <si>
-    <t>When a dog is described as solitary and independent, it means they might not be the most sociable playmate for other dogs.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as stalwart and vigilant?</t>
-  </si>
-  <si>
-    <t>A stalwart and vigilant dog is a natural protector, always on guard and ready to watch over its domain, and they tend to have a noticeable drooling level. While they do appreciate some mental stimulation, it isn't the most prominent aspect of their character.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as congenial and abundant?</t>
-  </si>
-  <si>
-    <t>A dog described as congenial and abundant is quite the socialite, generally getting along well with other canine companions. However, these pups also tend to have a noticeable drooling level and will shed a fair amount of fur, keeping you on your toes!</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as keen guardian?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> When a dog is described as a keen guardian, it means they display a noticeable protective and watchful nature, always keeping an eye out for their loved ones and territory.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  normal on active and engaged,  relatively high on sociable and adaptable,  quite low on solitary and independent,  slightly low on congenial and abundant´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster:```Members of this cluster can be described as:  quite low on active and engaged,  slightly low on mellow and serene,  slightly high on stalwart and vigilant,  slightly low on congenial and abundant´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster:```Members of this cluster can be described as:  relatively high on calm and relaxed,  relatively high on sociable and adaptable,  quite high on stalwart and vigilant,  relatively low on congenial and abundant´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and relaxed,  quite low on mellow and serene,  slightly low on solitary and independent,  normal on congenial and abundant´´´</t>
-  </si>
-  <si>
-    <t>Now, your task is to provide a description of a cluster.
-Make sure you continue to use the same format and style from the examples. 
-I am now going to give you one last description task to complete. 
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information, if any exists.
-The third sentence should describe the cluster’s specific weaknessess based on the available information, if any exists.
-Now do the same thing with the following: ```Members of this cluster can be described as:  normal on active and engaged,  slightly high on sociable and adaptable,  normal on stalwart and vigilant,  quite high on keen guardian´´´</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are highly protective and good with people, but tend to have a lower energy level and may struggle with other canine companions.
-Their strengths lie in their stalwart and vigilant nature, making them natural protectors of their domain, and their sociable and adaptable disposition, allowing them to be affectionate with families and charming with young children.
-However, a notable weakness is their calm and relaxed demeanor, which suggests less adaptability and trainability, coupled with a relatively low congeniality that means they might not get along well with other canine companions.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are predominantly calm and relaxed, favoring a quiet life with low energy, and while not highly independent, they also aren't strongly characterized by a moderate, serene demeanor. Their main strengths include their preference for a quiet, low-energy life, making them suitable companions for those seeking a less demanding pet, and they generally exhibit average sociability with other dogs. However, their high calm and relaxed nature means they may be less adaptable to new situations and challenging to train, and they are less likely to display a moderate, balanced energy level, potentially leaning towards a more sluggish disposition.</t>
-  </si>
-  <si>
-    <t>Now, your next task is to describe a specific dog based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the dog. The first sentence should use varied language to give an overview of the dog. The second sentence should describe the dog's specific strengths based on the metrics. The third sentence should describe aspects in which the dog is average and/or weak based on the statistics. Finally, summarize the dog with a single concluding statement. Here is the statistical description of the dog: ```Retrievers (Labrador) is extremely low on active and engaged. In particular, Retrievers (Labrador) indicates that Mental stimulation needs (on a scale of '1' to '5'). Retrievers (Labrador) is quite high on sociable and adaptable. Retrievers (Labrador) is quite low on solitary and independent. Retrievers (Labrador) is very low on congenial and abundant. In particular, Retrievers (Labrador) indicates that Drooling level (on a scale of '1' to '5'). ´´´ Here is the informative description of a dog belongs to: ```Retrievers (Labrador) is steadfast guard with the following characteristics: This cluster describes dogs that are generally low in energy and engagement, not particularly mellow, and are not very social with other dogs, but they do possess a degree of protective instinct. Their primary strength lies in their slightly elevated stalwart and vigilant trait, indicating a capacity for watchful and protective behavior that can be an asset for their home. However, they exhibit significant weaknesses in being quite low on active and engaged, meaning they are neither playful, bursting with energy, eager for mental stimulation, adaptable, nor easily trainable, and they tend to be less congenial with other canines.´´´</t>
-  </si>
-  <si>
-    <t>Labrador Retrievers are renowned for their affectionate nature towards people, yet they are dogs with remarkably low energy demands and limited interest in intense mental stimulation or extensive canine socializing. Their primary strength lies in their high sociability and adaptability with human families, making them charming and adjustable companions, coupled with a subtle underlying protective instinct. However, they are extremely low in active engagement and mental stimulation needs, tend to be less congenial with other dogs, and also exhibit a very low drooling level. Consequently, the Labrador Retriever is a loyal, human-centric dog that thrives in a calm environment rather than one requiring high energy, constant activity, or broad canine social interaction.</t>
-  </si>
-  <si>
-    <t>Thats really good. You truly understand the factors and names. 
-Now your task is to provide a description of a cluster.
-Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. 
-Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  normal on active and engaged,  relatively high on sociable and adaptable,  quite low on solitary and independent,  slightly low on congenial and abundant´´´</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are highly sociable and adaptable with humans, displaying average energy levels, and are generally easy to maintain.
-Their strengths include significant affection for their human families, charm with young children, and remarkable ease in adapting to new situations, alongside being less prone to shedding and drooling.
-However, they might exhibit a nuanced social dynamic with other dogs, as they are not solitary but are also slightly less congenial in canine companionship.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are generally low in energy and engagement, not particularly mellow, and are not very social with other dogs, but they do possess a degree of protective instinct.
-Their primary strength lies in their slightly elevated stalwart and vigilant trait, indicating a capacity for watchful and protective behavior that can be an asset for their home.
-However, they exhibit significant weaknesses in being quite low on active and engaged, meaning they are neither playful, bursting with energy, eager for mental stimulation, adaptable, nor easily trainable, and they tend to be less congenial with other canines.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are exceptionally protective and watchful, paired with a sociable and adaptable nature, while maintaining an average level of general activity.
-Their primary strengths lie in their quite high keen guardian instinct, making them highly vigilant protectors of their loved ones and territory, complemented by their slightly high sociability and adaptability, which allows them to be affectionate with families and adjust well to new surroundings.
-However, their 'normal' levels of active and engaged behavior and stalwart and vigilant traits suggest they may not always be bursting with energy or constantly demanding mental stimulation, and their protective nature, while strong, isn't necessarily paired with the most extreme, unwavering guarding beyond their inherent watchfulness.</t>
+    <t>A calm and relaxed dog isn't particularly playful or energetic, nor do they crave lots of mental stimulation. Instead, they are less adaptable and may not be the easiest to train.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as active and vigorous?</t>
+  </si>
+  <si>
+    <t>When a dog is described as active and vigorous, it means they are quite energetic and full of life!</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as adaptable and amiable?</t>
+  </si>
+  <si>
+    <t>When a dog is described as adaptable and amiable, they are cherished companions, known for being affectionate with their family and wonderfully good with young children. These easygoing pups also show a good level of adaptability to new situations, and they might even exhibit a certain degree of drooling.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as social and gentle?</t>
+  </si>
+  <si>
+    <t>A social and gentle dog is one that tends to get along well with other dogs, showing a friendly and agreeable nature in canine company.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as protective and robust?</t>
+  </si>
+  <si>
+    <t>When a dog is described as protective and robust, it means they possess a strong watchdog and protective nature, often accompanied by a notable drooling level. These dogs also tend to have a considerable need for mental stimulation to keep their minds engaged.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as self-contained and tidy?</t>
+  </si>
+  <si>
+    <t>A self-contained and tidy dog isn't one to leave trails of drool or shed hair all over the house. These neat companions are also quite amiable, generally getting along well with other dogs.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as alert and watchful?</t>
+  </si>
+  <si>
+    <t>An alert and watchful dog is a true guardian, always ready to act as a watchdog with a strong protective nature.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are highly affectionate and adaptable with their human families, but tend to be less sociable with other dogs and are not particularly self-contained or tidy. Their primary strengths lie in their exceptional adaptability to new situations and their amiable nature, making them wonderfully affectionate with their family and good with young children. However, they exhibit significant weaknesses in their interactions with other dogs, often struggling to be social and gentle, and are also slightly less self-contained or tidy, indicating a tendency to drool or shed.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are generally low in playfulness and energy, not particularly active, but possess some protective instincts and may not be the tidiest companions. Their specific strengths lie in their slightly elevated protective and robust nature, offering a degree of watchdog capability, and they are less demanding in terms of constant physical activity or high-energy play. However, they exhibit weaknesses in their very low playfulness and energy, are not particularly active, may not get along well with other dogs, can be prone to shedding or drooling, and are not quick to learn or highly adaptable.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are dedicated protective guardians and affectionate family members, characterized by a calm disposition but a tendency to be less self-contained. Their key strengths include a strong watchdog and protective nature, deep affection for family and children due to their adaptable and amiable temperament, and a generally calm demeanor that doesn't demand constant high-energy play. However, their calm nature can mean they are less quick to learn new tricks or adapt to completely novel scenarios, and they are prone to drooling and shedding, as indicated by their lower self-contained and tidy score, which also implies they may not be as amicable with other dogs.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are primarily calm and relaxed, exhibiting very low energy levels, and showing a slight disinclination towards social interactions with other canines. Their primary strength lies in their profoundly calm and relaxed nature, making them ideal companions for individuals seeking a tranquil, low-energy pet that requires minimal physical or mental stimulation. However, they are notably unsuited for highly active households, may be less adaptable or quick to learn new things, and tend to be less social and gentle in their interactions with other dogs.</t>
+  </si>
+  <si>
+    <t>This cluster describes dogs that are notably alert and watchful guardians, combining a good level of adaptability and affection with average energy and protective traits. Their primary strengths lie in their exceptional vigilance as watchdogs and protectors, complemented by their affectionate nature towards family and children, and their good adaptability to new situations. While generally well-rounded, their energy levels are only at a normal level, meaning they are not particularly bursting with playfulness or requiring constant high-energy activities.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as adaptable companion?</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as calm guard?</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as devoted guardian?</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as peaceful pet?</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as protective friend?</t>
+  </si>
+  <si>
+    <t>German Shepherd Dogs are primarily known for their steadfast protective instincts, exhibiting a more reserved demeanor rather than high energy or boisterous playfulness. Their most prominent strength lies in their very high protective and robust nature, making them exceptional watchdogs, complemented by an average level of activity and alertness. However, a significant weakness is their very low playfulness and energy, indicating they are not prone to burst with activity or demand constant mental stimulation. Ultimately, the German Shepherd Dog is a dedicated and watchful companion better suited for a stable home environment than one requiring high-energy frolics.</t>
+  </si>
+  <si>
+    <t>Fantastic! That’s exactly what I needed.
+Now, let’s return to your analysis. Your next task is to describe a specific dog based on the provided information.
+Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the dog. 
+The first sentence should use varied language to give an overview of the dog. 
+The second sentence should describe the dog's specific strengths based on the metrics. 
+The third sentence should describe aspects in which the dog is average and/or weak based on the statistics. 
+Finally, summarize the dog with a single concluding statement. 
+Here is the statistical description of the dog: ```German Shepherd Dogs is very low on playful and energetic. In particular, German Shepherd Dogs indicates that Playfulness level (on a scale of '1' to '5'). German Shepherd Dogs is average on active and vigorous. German Shepherd Dogs is very high on protective and robust. In particular, German Shepherd Dogs indicates that Watchdog and protective nature (on a scale of '1' to '5'). German Shepherd Dogs is average on alert and watchful. ´´´ 
+Here is the informative description of a dog belongs to: ```German Shepherd Dogs is calm guard with the following characteristics: This cluster describes dogs that are generally low in playfulness and energy, not particularly active, but possess some protective instincts and may not be the tidiest companions.
+Their specific strengths lie in their slightly elevated protective and robust nature, offering a degree of watchdog capability, and they are less demanding in terms of constant physical activity or high-energy play.
+However, they exhibit weaknesses in their very low playfulness and energy, are not particularly active, may not get along well with other dogs, can be prone to shedding or drooling, and are not quick to learn or highly adaptable.´´´</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of the dog: ```Dalmatians is average on playful and energetic. Dalmatians is average on active and vigorous. Dalmatians is quite high on protective and robust. Dalmatians is average on alert and watchful. ´´´ 
+Here is the informative description of a dog belongs to: ```Dalmatians is calm guard with the following characteristics: This cluster describes dogs that are generally low in playfulness and energy, not particularly active, but possess some protective instincts and may not be the tidiest companions.
+Their specific strengths lie in their slightly elevated protective and robust nature, offering a degree of watchdog capability, and they are less demanding in terms of constant physical activity or high-energy play.
+However, they exhibit weaknesses in their very low playfulness and energy, are not particularly active, may not get along well with other dogs, can be prone to shedding or drooling, and are not quick to learn or highly adaptable.´´´</t>
+  </si>
+  <si>
+    <t>Dalmatians are a distinctive breed that blends an active and playful spirit with a notably protective and robust demeanor. Their primary strength lies in their quite high protective and robust nature, making them vigilant and capable guardians for their home. While possessing a strong protective instinct, Dalmatians exhibit average levels of playfulness, energy, and alertness, suggesting they are neither exceptionally exuberant nor overly cautious. Overall, the Dalmatian is a balanced companion with a strong guarding instinct, suited for those seeking a dog with moderate energy and a watchful presence.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,20 +149,321 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -179,38 +472,212 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -233,44 +700,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -297,14 +764,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -331,6 +816,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -342,166 +845,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -510,8 +989,8 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="94" style="2" customWidth="1"/>
-    <col min="2" max="2" width="98.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="76.54296875" customWidth="1"/>
+    <col min="2" max="2" width="92.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -522,39 +1001,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -562,7 +1041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="20" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -570,7 +1049,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="20" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -578,7 +1057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -586,64 +1065,64 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="50" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="50" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="50" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="40" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="190" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="87" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    <row r="16" spans="1:2" ht="100" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/describe/few_shot/final_summary/messages_dog.xlsx
+++ b/data/describe/few_shot/final_summary/messages_dog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9854ACEF-BCF9-416C-BA38-0A5F4C8F9589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02707192-A879-4393-9E4B-E4C7FCEDE8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53295" yWindow="2640" windowWidth="23370" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>User</t>
   </si>
@@ -33,85 +33,67 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a dog is described as playful and energetic?</t>
-  </si>
-  <si>
-    <t>When a dog is described as playful and energetic, it means they are truly a bundle of joy, bursting with playfulness and high energy, always eager for fun and in need of exciting mental challenges to keep their clever mind engaged. These lively pups are also incredibly adaptable, ready to embrace new experiences, and respond well to training.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as calm and relaxed?</t>
-  </si>
-  <si>
-    <t>A calm and relaxed dog isn't particularly playful or energetic, nor do they crave lots of mental stimulation. Instead, they are less adaptable and may not be the easiest to train.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as active and vigorous?</t>
-  </si>
-  <si>
-    <t>When a dog is described as active and vigorous, it means they are quite energetic and full of life!</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as adaptable and amiable?</t>
-  </si>
-  <si>
-    <t>When a dog is described as adaptable and amiable, they are cherished companions, known for being affectionate with their family and wonderfully good with young children. These easygoing pups also show a good level of adaptability to new situations, and they might even exhibit a certain degree of drooling.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as social and gentle?</t>
-  </si>
-  <si>
-    <t>A social and gentle dog is one that tends to get along well with other dogs, showing a friendly and agreeable nature in canine company.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as protective and robust?</t>
-  </si>
-  <si>
-    <t>When a dog is described as protective and robust, it means they possess a strong watchdog and protective nature, often accompanied by a notable drooling level. These dogs also tend to have a considerable need for mental stimulation to keep their minds engaged.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as self-contained and tidy?</t>
-  </si>
-  <si>
-    <t>A self-contained and tidy dog isn't one to leave trails of drool or shed hair all over the house. These neat companions are also quite amiable, generally getting along well with other dogs.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as alert and watchful?</t>
-  </si>
-  <si>
-    <t>An alert and watchful dog is a true guardian, always ready to act as a watchdog with a strong protective nature.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are highly affectionate and adaptable with their human families, but tend to be less sociable with other dogs and are not particularly self-contained or tidy. Their primary strengths lie in their exceptional adaptability to new situations and their amiable nature, making them wonderfully affectionate with their family and good with young children. However, they exhibit significant weaknesses in their interactions with other dogs, often struggling to be social and gentle, and are also slightly less self-contained or tidy, indicating a tendency to drool or shed.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are generally low in playfulness and energy, not particularly active, but possess some protective instincts and may not be the tidiest companions. Their specific strengths lie in their slightly elevated protective and robust nature, offering a degree of watchdog capability, and they are less demanding in terms of constant physical activity or high-energy play. However, they exhibit weaknesses in their very low playfulness and energy, are not particularly active, may not get along well with other dogs, can be prone to shedding or drooling, and are not quick to learn or highly adaptable.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are dedicated protective guardians and affectionate family members, characterized by a calm disposition but a tendency to be less self-contained. Their key strengths include a strong watchdog and protective nature, deep affection for family and children due to their adaptable and amiable temperament, and a generally calm demeanor that doesn't demand constant high-energy play. However, their calm nature can mean they are less quick to learn new tricks or adapt to completely novel scenarios, and they are prone to drooling and shedding, as indicated by their lower self-contained and tidy score, which also implies they may not be as amicable with other dogs.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are primarily calm and relaxed, exhibiting very low energy levels, and showing a slight disinclination towards social interactions with other canines. Their primary strength lies in their profoundly calm and relaxed nature, making them ideal companions for individuals seeking a tranquil, low-energy pet that requires minimal physical or mental stimulation. However, they are notably unsuited for highly active households, may be less adaptable or quick to learn new things, and tend to be less social and gentle in their interactions with other dogs.</t>
-  </si>
-  <si>
-    <t>This cluster describes dogs that are notably alert and watchful guardians, combining a good level of adaptability and affection with average energy and protective traits. Their primary strengths lie in their exceptional vigilance as watchdogs and protectors, complemented by their affectionate nature towards family and children, and their good adaptability to new situations. While generally well-rounded, their energy levels are only at a normal level, meaning they are not particularly bursting with playfulness or requiring constant high-energy activities.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as adaptable companion?</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as calm guard?</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as devoted guardian?</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as peaceful pet?</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as protective friend?</t>
-  </si>
-  <si>
-    <t>German Shepherd Dogs are primarily known for their steadfast protective instincts, exhibiting a more reserved demeanor rather than high energy or boisterous playfulness. Their most prominent strength lies in their very high protective and robust nature, making them exceptional watchdogs, complemented by an average level of activity and alertness. However, a significant weakness is their very low playfulness and energy, indicating they are not prone to burst with activity or demand constant mental stimulation. Ultimately, the German Shepherd Dog is a dedicated and watchful companion better suited for a stable home environment than one requiring high-energy frolics.</t>
+    <t>What does it mean when a dog is described as active?</t>
+  </si>
+  <si>
+    <t>When a dog is described as active, it means that they have a high level of playfulness, energy, and need for mental stimulation, making them lively companions who thrive on interaction and exercise. Additionally, their strong adaptability and trainability suggest they are eager to engage with their environment and learn new things, making them dynamic members of any household.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as not active?</t>
+  </si>
+  <si>
+    <t>When a dog is described as not active, it means they are not playful, lack energy, and have minimal need for mental stimulation. This type of dog tends to prefer a more relaxed lifestyle, showing little enthusiasm for physical activities and having low adaptability to new environments.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as energetic?</t>
+  </si>
+  <si>
+    <t>When a dog is described as energetic, it means they have a lively spirit and a noticeable energy level that makes them eager to play and explore. This enthusiasm for activity can bring a sense of joy and vitality to any environment, making them the perfect companions for those who love an active lifestyle!</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as adaptable?</t>
+  </si>
+  <si>
+    <t>When a dog is described as adaptable, it means that the dog can adjust to various situations and environments with relative ease, although not in an outstanding or highly noticeable way. This versatility includes being affectionate with family, getting along well with young children, and showing some flexibility when it comes to different experiences, all while possibly having a bit of drooling on the side.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as sociable?</t>
+  </si>
+  <si>
+    <t>When a dog is described as sociable, it means they have a friendly demeanor and get along well with other dogs, even if this trait is only slightly pronounced. This sociable nature makes them more inclined to engage positively with their furry friends, showcasing a willingness to socialize and play.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as watchful?</t>
+  </si>
+  <si>
+    <t>When a dog is described as watchful, it means that they have a protective nature and are attentive to their surroundings, making them alert watchdogs. Additionally, they may have a tendency to drool at times, and while they might not require excessive mental stimulation, they still keep a keen eye on whatâ€™s happening around them.</t>
+  </si>
+  <si>
+    <t>When a dog is described as sociable, it means they are open to interaction with others, even if their level of friendliness with other dogs is only mild. This sociable nature might also show in playful drooling and shedding, hinting at a relaxed demeanor that enjoys companionship.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as reserved?</t>
+  </si>
+  <si>
+    <t>When a dog is described as reserved, it indicates that they tend to be more independent and cautious, showing a protective nature that makes them alert as a watchdog. This means they might not seek out the company of other dogs as eagerly and are likely to be more selective about their interactions.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as easy companion?</t>
+  </si>
+  <si>
+    <t>This cluster comprises dogs that exhibit a more laid-back demeanor, being slightly high on not being active while also displaying adaptability and watchfulness. A strength of this group lies in their adaptability, making them suitable for a variety of living situations and environments while maintaining a watchful eye on their surroundings. However, they may struggle in social settings, as their relatively low sociability could hinder interactions with other dogs and people.</t>
+  </si>
+  <si>
+    <t>This cluster consists of dogs that exhibit lower levels of activity and energy, presenting a more laid-back demeanor. They tend to be reasonably sociable, indicating that while they may not be the most outgoing, they are generally friendly in social situations. However, their relatively low scores on both active and energetic suggest they may not thrive in high-energy environments or require less physical engagement, which could limit their appeal to more active households.</t>
+  </si>
+  <si>
+    <t>This cluster represents dogs that are generally less active, displaying a balanced adaptability, while tending to be more reserved. Their specific strength lies in their adaptability, which allows them to adjust well to various environments and situations. However, their slight lack of sociability may limit their interactions with people and other dogs, potentially hindering social development and companionship.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as relaxed observer?</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as calm adapter?</t>
   </si>
   <si>
     <t>Fantastic! That’s exactly what I needed.
@@ -121,26 +103,24 @@
 The second sentence should describe the dog's specific strengths based on the metrics. 
 The third sentence should describe aspects in which the dog is average and/or weak based on the statistics. 
 Finally, summarize the dog with a single concluding statement. 
-Here is the statistical description of the dog: ```German Shepherd Dogs is very low on playful and energetic. In particular, German Shepherd Dogs indicates that Playfulness level (on a scale of '1' to '5'). German Shepherd Dogs is average on active and vigorous. German Shepherd Dogs is very high on protective and robust. In particular, German Shepherd Dogs indicates that Watchdog and protective nature (on a scale of '1' to '5'). German Shepherd Dogs is average on alert and watchful. ´´´ 
-Here is the informative description of a dog belongs to: ```German Shepherd Dogs is calm guard with the following characteristics: This cluster describes dogs that are generally low in playfulness and energy, not particularly active, but possess some protective instincts and may not be the tidiest companions.
-Their specific strengths lie in their slightly elevated protective and robust nature, offering a degree of watchdog capability, and they are less demanding in terms of constant physical activity or high-energy play.
-However, they exhibit weaknesses in their very low playfulness and energy, are not particularly active, may not get along well with other dogs, can be prone to shedding or drooling, and are not quick to learn or highly adaptable.´´´</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of the dog: ```Dalmatians is average on playful and energetic. Dalmatians is average on active and vigorous. Dalmatians is quite high on protective and robust. Dalmatians is average on alert and watchful. ´´´ 
-Here is the informative description of a dog belongs to: ```Dalmatians is calm guard with the following characteristics: This cluster describes dogs that are generally low in playfulness and energy, not particularly active, but possess some protective instincts and may not be the tidiest companions.
-Their specific strengths lie in their slightly elevated protective and robust nature, offering a degree of watchdog capability, and they are less demanding in terms of constant physical activity or high-energy play.
-However, they exhibit weaknesses in their very low playfulness and energy, are not particularly active, may not get along well with other dogs, can be prone to shedding or drooling, and are not quick to learn or highly adaptable.´´´</t>
-  </si>
-  <si>
-    <t>Dalmatians are a distinctive breed that blends an active and playful spirit with a notably protective and robust demeanor. Their primary strength lies in their quite high protective and robust nature, making them vigilant and capable guardians for their home. While possessing a strong protective instinct, Dalmatians exhibit average levels of playfulness, energy, and alertness, suggesting they are neither exceptionally exuberant nor overly cautious. Overall, the Dalmatian is a balanced companion with a strong guarding instinct, suited for those seeking a dog with moderate energy and a watchful presence.</t>
+Here is the statistical description of Beagles: ```Beagles is average on active. Beagles is quite low on energetic. Beagles is very low on sociable. In particular, Beagles indicates that Good with other dogs (on a scale of '1' to '5'). Beagles is very low on sociable. In particular, Beagles indicates that Drooling level (on a scale of '1' to '5'). ´´´ 
+Here is the informative description of Beagles: ```Beagles is calm companion with the following characteristics: This cluster consists of dogs that exhibit a more subdued nature, characterized by their relatively low activity levels and energy. A notable strength of this cluster is that despite being low on activity, these dogs maintain a normal sociable demeanor, allowing them to interact without being overly boisterous. However, their specific weakness lies in their lower levels of sociability, which may lead to challenges in forming strong connections with other dogs and people.´´´</t>
+  </si>
+  <si>
+    <t>Beagles are characterized as calm companions that exhibit a more reserved and composed demeanor. Their notable strength lies in their ability to get along well with other dogs, showcasing a good temperament in social situations. However, Beagles are average on activity levels and exhibit low energy and sociability, which could hinder their engagement in more active play or social interactions. Overall, Beagles are gentle and good-natured dogs that thrive in serene environments.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of French Bulldogs: ```French Bulldogs is quite low on active. French Bulldogs is extremely high on adaptable. In particular, French Bulldogs indicates that Affectionate with family (on a scale of '1' to '5'). French Bulldogs is quite low on sociable. French Bulldogs is average on sociable. ´´´ Here is the informative description of French Bulldogs: ```French Bulldogs is versatile companion with the following characteristics: This cluster consists of dogs that exhibit a unique balance of traits, characterized by a relatively low level of sociability and a high degree of adaptability. Their adaptability suggests that they can thrive in a variety of environments and circumstances, making them versatile companions. However, their tendency to be less sociable may limit their interactions with both humans and other animals, resulting in a more reserved demeanor.´´´</t>
+  </si>
+  <si>
+    <t>French Bulldogs are distinct dogs known for their adaptability and affectionate nature within the family. Their remarkable strength lies in their high adaptability, allowing them to adjust well to different living situations and environments. However, they display lower levels of sociability, which can create challenges in forming connections with strangers or other pets. Overall, French Bulldogs thrive as versatile companions, especially suited for families who appreciate their loving demeanor yet may need to navigate their reserved temperament in social settings.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,10 +256,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -623,12 +611,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -986,11 +977,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="76.54296875" customWidth="1"/>
-    <col min="2" max="2" width="92.08984375" customWidth="1"/>
+    <col min="1" max="1" width="64.08984375" customWidth="1"/>
+    <col min="2" max="2" width="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1001,7 +992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1009,7 +1000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="36" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1017,7 +1008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1025,7 +1016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1033,7 +1024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1041,7 +1032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1049,76 +1040,60 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="48" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="42" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="210" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+    </row>
+    <row r="14" spans="1:2" ht="94.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="190" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="100" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/final_summary/messages_dog.xlsx
+++ b/data/describe/few_shot/final_summary/messages_dog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02707192-A879-4393-9E4B-E4C7FCEDE8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBD244A-3836-404E-9EFB-68B6F5E4E645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,9 +66,6 @@
     <t>What does it mean when a dog is described as watchful?</t>
   </si>
   <si>
-    <t>When a dog is described as watchful, it means that they have a protective nature and are attentive to their surroundings, making them alert watchdogs. Additionally, they may have a tendency to drool at times, and while they might not require excessive mental stimulation, they still keep a keen eye on whatâ€™s happening around them.</t>
-  </si>
-  <si>
     <t>When a dog is described as sociable, it means they are open to interaction with others, even if their level of friendliness with other dogs is only mild. This sociable nature might also show in playful drooling and shedding, hinting at a relaxed demeanor that enjoys companionship.</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>French Bulldogs are distinct dogs known for their adaptability and affectionate nature within the family. Their remarkable strength lies in their high adaptability, allowing them to adjust well to different living situations and environments. However, they display lower levels of sociability, which can create challenges in forming connections with strangers or other pets. Overall, French Bulldogs thrive as versatile companions, especially suited for families who appreciate their loving demeanor yet may need to navigate their reserved temperament in social settings.</t>
+  </si>
+  <si>
+    <t>When a dog is described as watchful, it means that they have a protective nature and are attentive to their surroundings, making them alert watchdogs. Additionally, they may have a tendency to drool at times, and while they might not require excessive mental stimulation, they still keep a keen eye on what's happening around them.</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1037,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="36" x14ac:dyDescent="0.35">
@@ -1045,55 +1045,55 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="48" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="42" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="210" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="94.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/final_summary/messages_dog.xlsx
+++ b/data/describe/few_shot/final_summary/messages_dog.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBD244A-3836-404E-9EFB-68B6F5E4E645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB14890B-6A57-4FF5-998A-1BF572065C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
-    <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
+    <sheet name="messages_dogs" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>User</t>
   </si>
@@ -33,94 +33,83 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a dog is described as active?</t>
-  </si>
-  <si>
-    <t>When a dog is described as active, it means that they have a high level of playfulness, energy, and need for mental stimulation, making them lively companions who thrive on interaction and exercise. Additionally, their strong adaptability and trainability suggest they are eager to engage with their environment and learn new things, making them dynamic members of any household.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as not active?</t>
-  </si>
-  <si>
-    <t>When a dog is described as not active, it means they are not playful, lack energy, and have minimal need for mental stimulation. This type of dog tends to prefer a more relaxed lifestyle, showing little enthusiasm for physical activities and having low adaptability to new environments.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as energetic?</t>
-  </si>
-  <si>
-    <t>When a dog is described as energetic, it means they have a lively spirit and a noticeable energy level that makes them eager to play and explore. This enthusiasm for activity can bring a sense of joy and vitality to any environment, making them the perfect companions for those who love an active lifestyle!</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as adaptable?</t>
-  </si>
-  <si>
-    <t>When a dog is described as adaptable, it means that the dog can adjust to various situations and environments with relative ease, although not in an outstanding or highly noticeable way. This versatility includes being affectionate with family, getting along well with young children, and showing some flexibility when it comes to different experiences, all while possibly having a bit of drooling on the side.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as sociable?</t>
-  </si>
-  <si>
-    <t>When a dog is described as sociable, it means they have a friendly demeanor and get along well with other dogs, even if this trait is only slightly pronounced. This sociable nature makes them more inclined to engage positively with their furry friends, showcasing a willingness to socialize and play.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as watchful?</t>
-  </si>
-  <si>
-    <t>When a dog is described as sociable, it means they are open to interaction with others, even if their level of friendliness with other dogs is only mild. This sociable nature might also show in playful drooling and shedding, hinting at a relaxed demeanor that enjoys companionship.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as reserved?</t>
-  </si>
-  <si>
-    <t>When a dog is described as reserved, it indicates that they tend to be more independent and cautious, showing a protective nature that makes them alert as a watchdog. This means they might not seek out the company of other dogs as eagerly and are likely to be more selective about their interactions.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as easy companion?</t>
-  </si>
-  <si>
-    <t>This cluster comprises dogs that exhibit a more laid-back demeanor, being slightly high on not being active while also displaying adaptability and watchfulness. A strength of this group lies in their adaptability, making them suitable for a variety of living situations and environments while maintaining a watchful eye on their surroundings. However, they may struggle in social settings, as their relatively low sociability could hinder interactions with other dogs and people.</t>
-  </si>
-  <si>
-    <t>This cluster consists of dogs that exhibit lower levels of activity and energy, presenting a more laid-back demeanor. They tend to be reasonably sociable, indicating that while they may not be the most outgoing, they are generally friendly in social situations. However, their relatively low scores on both active and energetic suggest they may not thrive in high-energy environments or require less physical engagement, which could limit their appeal to more active households.</t>
-  </si>
-  <si>
-    <t>This cluster represents dogs that are generally less active, displaying a balanced adaptability, while tending to be more reserved. Their specific strength lies in their adaptability, which allows them to adjust well to various environments and situations. However, their slight lack of sociability may limit their interactions with people and other dogs, potentially hindering social development and companionship.</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as relaxed observer?</t>
-  </si>
-  <si>
-    <t>What does it mean when a dog is described as calm adapter?</t>
-  </si>
-  <si>
-    <t>Fantastic! That’s exactly what I needed.
-Now, let’s return to your analysis. Your next task is to describe a specific dog based on the provided information.
-Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the dog. 
-The first sentence should use varied language to give an overview of the dog. 
-The second sentence should describe the dog's specific strengths based on the metrics. 
-The third sentence should describe aspects in which the dog is average and/or weak based on the statistics. 
-Finally, summarize the dog with a single concluding statement. 
-Here is the statistical description of Beagles: ```Beagles is average on active. Beagles is quite low on energetic. Beagles is very low on sociable. In particular, Beagles indicates that Good with other dogs (on a scale of '1' to '5'). Beagles is very low on sociable. In particular, Beagles indicates that Drooling level (on a scale of '1' to '5'). ´´´ 
-Here is the informative description of Beagles: ```Beagles is calm companion with the following characteristics: This cluster consists of dogs that exhibit a more subdued nature, characterized by their relatively low activity levels and energy. A notable strength of this cluster is that despite being low on activity, these dogs maintain a normal sociable demeanor, allowing them to interact without being overly boisterous. However, their specific weakness lies in their lower levels of sociability, which may lead to challenges in forming strong connections with other dogs and people.´´´</t>
-  </si>
-  <si>
-    <t>Beagles are characterized as calm companions that exhibit a more reserved and composed demeanor. Their notable strength lies in their ability to get along well with other dogs, showcasing a good temperament in social situations. However, Beagles are average on activity levels and exhibit low energy and sociability, which could hinder their engagement in more active play or social interactions. Overall, Beagles are gentle and good-natured dogs that thrive in serene environments.</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of French Bulldogs: ```French Bulldogs is quite low on active. French Bulldogs is extremely high on adaptable. In particular, French Bulldogs indicates that Affectionate with family (on a scale of '1' to '5'). French Bulldogs is quite low on sociable. French Bulldogs is average on sociable. ´´´ Here is the informative description of French Bulldogs: ```French Bulldogs is versatile companion with the following characteristics: This cluster consists of dogs that exhibit a unique balance of traits, characterized by a relatively low level of sociability and a high degree of adaptability. Their adaptability suggests that they can thrive in a variety of environments and circumstances, making them versatile companions. However, their tendency to be less sociable may limit their interactions with both humans and other animals, resulting in a more reserved demeanor.´´´</t>
-  </si>
-  <si>
-    <t>French Bulldogs are distinct dogs known for their adaptability and affectionate nature within the family. Their remarkable strength lies in their high adaptability, allowing them to adjust well to different living situations and environments. However, they display lower levels of sociability, which can create challenges in forming connections with strangers or other pets. Overall, French Bulldogs thrive as versatile companions, especially suited for families who appreciate their loving demeanor yet may need to navigate their reserved temperament in social settings.</t>
-  </si>
-  <si>
-    <t>When a dog is described as watchful, it means that they have a protective nature and are attentive to their surroundings, making them alert watchdogs. Additionally, they may have a tendency to drool at times, and while they might not require excessive mental stimulation, they still keep a keen eye on what's happening around them.</t>
+    <t>What does it mean when a dog is described as short and sleek?</t>
+  </si>
+  <si>
+    <t>When a dog is described as short and sleek, picture a pup whose coat is wonderfully short and incredibly smooth to the touch.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as medium and layered?</t>
+  </si>
+  <si>
+    <t>A dog described as medium and layered boasts a beautiful medium-length double coat. Keeping this stunning coat in top condition means that its grooming frequency is a consideration.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as neat and simple?</t>
+  </si>
+  <si>
+    <t>A neat and simple dog is one that sports a coat that is either short or medium in length.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as flowing and maintained?</t>
+  </si>
+  <si>
+    <t>A dog with a flowing and maintained look boasts a long coat that absolutely demands regular grooming to keep it pristine. This magnificent mane often has a beautiful, silky texture.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as calm and placid?</t>
+  </si>
+  <si>
+    <t>When a dog is described as calm and placid, it means that the dog is not spirited and responsive. Instead of seeking mental stimulation, playfulness, or high energy, a calm and placid dog embodies a serene and relaxed demeanor, embracing a peaceful existence without the urge for excitement or activity.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as spirited and responsive?</t>
+  </si>
+  <si>
+    <t>When a dog is described as spirited and responsive, it means they are full of energy and enthusiasm, always eager for play and mental challenges. With high levels of playfulness, energy, and a keen need for mental stimulation, they are not just lively companions but also quick to learn and adapt, making them delightful and engaging pets.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as genial and adjustable?</t>
+  </si>
+  <si>
+    <t>When a dog is described as genial and adjustable, it means this furry friend is welcoming and friendly, showing an openness to strangers that makes them a joy to be around. They are also adaptable, able to adjust to various situations, such as being good with young children and other dogs, which adds a playful energy to their personality.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as inquisitive and bright?</t>
+  </si>
+  <si>
+    <t>When a dog is described as inquisitive and bright, it means that this furry friend has a curious nature and an eagerness to explore the world around them. Their need for mental stimulation reflects their intelligent and alert personality, hinting at a playful mind that thrives on discovering new things!</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as versatile companion?</t>
+  </si>
+  <si>
+    <t>These dogs possess a medium and layered appearance, indicating a balanced and versatile physical trait. Strengths of this cluster include their adaptability, which may allow them to thrive in various environments and roles. However, they may struggle with being overly neat and simple, as well as a tendency towards less calmness and placidity, potentially leading to a more energetic or chaotic demeanor.</t>
+  </si>
+  <si>
+    <t>What does it mean when a dog is described as adventurous friend?</t>
+  </si>
+  <si>
+    <t>These dogs are characterized by their spirited and responsive nature, as well as their inquisitive and bright demeanor. Their strengths lie in their high levels of energy and curiosity, making them engaging companions that are eager to explore their surroundings and interact with people. However, they may struggle with being less neat and simple in their appearance, as well as having a lower tendency to exhibit a short and sleek coat, which could be perceived as a lack of polish in their overall presentation.</t>
+  </si>
+  <si>
+    <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific dog based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the dog. The first sentence should use varied language to give an overview of the dog. The second sentence should describe the dog's specific strengths based on the metrics. The third sentence should describe aspects in which the dog is average and/or weak based on the statistics. Finally, summarize the dog with a single concluding statement. Here is the statistical description of French Bulldogs: ```French Bulldogs is very low on short and sleek. Notably, French Bulldogs has characteristics related to 'the coat type is smooth'. French Bulldogs is average on neat and simple. French Bulldogs is average on calm and placid. French Bulldogs is extremely low on genial and adjustable. Notably, French Bulldogs has characteristics related to 'good with other dogs'. ´´´ Here is the informative description of French Bulldogs: ```French Bulldogs is spirited companion with the following characteristics: This cluster is composed of dogs that exhibit a generally less refined appearance and a more spirited temperament. Their unique strengths may lie in their adaptability, as they are less likely to conform to simplistic or tidy expectations. However, their weaknesses include a tendency to be less calm and balanced, potentially causing challenges in high-stress environments.´´´</t>
+  </si>
+  <si>
+    <t>French Bulldogs are charming companions known for their spirited demeanor and distinctive appearance. They exhibit a smooth coat and have a notable strength in being good with other dogs, fostering positive interactions in social settings. However, they tend to be less genial and adjustable, and while they are average in calmness, they may struggle in high-stress situations. Overall, French Bulldogs embody a unique blend of spirited energy and adaptability, making them engaging pets.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of Beagles: ```Beagles is very low on short and sleek. Notably, Beagles has characteristics related to 'the coat type is smooth'. Beagles is average on neat and simple. Beagles is average on spirited and responsive. Beagles is average on genial and adjustable. ´´´ Here is the informative description of Beagles: ```Beagles is adventurous friend with the following characteristics: This cluster represents dogs that are characterized by their spirited and responsive nature, as well as their inquisitive and bright demeanor. Their strengths lie in their high levels of energy and curiosity, making them engaging companions that are eager to explore their surroundings and interact with people. However, they may struggle with being less neat and simple in their appearance, as well as having a lower tendency to exhibit a short and sleek coat, which could be perceived as a lack of polish in their overall presentation.´´´</t>
+  </si>
+  <si>
+    <t>Beagles are vibrant and curious dogs known for their adventurous spirit. Their strengths lie in their spirited and responsive nature, which makes them enthusiastic companions eager to explore the world around them. However, they tend to be average in terms of neatness and simplicity of appearance, and they have a lower likelihood of having a short and sleek coat. Overall, Beagles embody the essence of an adventurous friend, bringing energy and engagement to any environment.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,20 +240,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -611,17 +586,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -976,128 +942,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="64.08984375" customWidth="1"/>
-    <col min="2" max="2" width="67" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="36" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="36" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="48" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="42" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="210" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="94.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>